--- a/wolf/Excel/Language_小镇多语言.xlsx
+++ b/wolf/Excel/Language_小镇多语言.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="1562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="1574">
   <si>
     <t>Int</t>
   </si>
@@ -3655,156 +3655,159 @@
     <t>Collection</t>
   </si>
   <si>
+    <t>保存穿搭</t>
+  </si>
+  <si>
+    <t>Text_Tab1_4</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>测试</t>
+  </si>
+  <si>
+    <t>Text_Tab2_101</t>
+  </si>
+  <si>
+    <t>Body Type</t>
+  </si>
+  <si>
+    <t>体型</t>
+  </si>
+  <si>
+    <t>Text_Tab2_102</t>
+  </si>
+  <si>
+    <t>Skin Tone</t>
+  </si>
+  <si>
+    <t>肤色</t>
+  </si>
+  <si>
+    <t>Text_Tab2_103</t>
+  </si>
+  <si>
+    <t>Face</t>
+  </si>
+  <si>
+    <t>脸型</t>
+  </si>
+  <si>
+    <t>Text_Tab2_104</t>
+  </si>
+  <si>
+    <t>Eyes</t>
+  </si>
+  <si>
+    <t>眼睛</t>
+  </si>
+  <si>
+    <t>Text_Tab2_105</t>
+  </si>
+  <si>
+    <t>Eyebrows</t>
+  </si>
+  <si>
+    <t>眉毛</t>
+  </si>
+  <si>
+    <t>Text_Tab2_106</t>
+  </si>
+  <si>
+    <t>Makeup</t>
+  </si>
+  <si>
+    <t>妆容</t>
+  </si>
+  <si>
+    <t>Text_Tab2_107</t>
+  </si>
+  <si>
+    <t>Expression</t>
+  </si>
+  <si>
+    <t>表情</t>
+  </si>
+  <si>
+    <t>Text_Tab2_108</t>
+  </si>
+  <si>
+    <t>Outfit</t>
+  </si>
+  <si>
+    <t>套装</t>
+  </si>
+  <si>
+    <t>Text_Tab2_109</t>
+  </si>
+  <si>
+    <t>Hair</t>
+  </si>
+  <si>
+    <t>头发</t>
+  </si>
+  <si>
+    <t>Text_Tab2_110</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>上衣</t>
+  </si>
+  <si>
+    <t>Text_Tab2_111</t>
+  </si>
+  <si>
+    <t>Bottom</t>
+  </si>
+  <si>
+    <t>下衣</t>
+  </si>
+  <si>
+    <t>Text_Tab2_112</t>
+  </si>
+  <si>
+    <t>Gloves</t>
+  </si>
+  <si>
+    <t>鞋子</t>
+  </si>
+  <si>
+    <t>Text_Tab2_113</t>
+  </si>
+  <si>
+    <t>Shoes</t>
+  </si>
+  <si>
+    <t>手套</t>
+  </si>
+  <si>
+    <t>Text_Tab2_114</t>
+  </si>
+  <si>
+    <t>Pet</t>
+  </si>
+  <si>
+    <t>宠物</t>
+  </si>
+  <si>
+    <t>Text_Tab2_115</t>
+  </si>
+  <si>
+    <t>Accessory</t>
+  </si>
+  <si>
+    <t>饰品</t>
+  </si>
+  <si>
+    <t>Text_Tab2_501</t>
+  </si>
+  <si>
     <t>收藏</t>
   </si>
   <si>
-    <t>Text_Tab1_4</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>测试</t>
-  </si>
-  <si>
-    <t>Text_Tab2_101</t>
-  </si>
-  <si>
-    <t>Body Type</t>
-  </si>
-  <si>
-    <t>体型</t>
-  </si>
-  <si>
-    <t>Text_Tab2_102</t>
-  </si>
-  <si>
-    <t>Skin Tone</t>
-  </si>
-  <si>
-    <t>肤色</t>
-  </si>
-  <si>
-    <t>Text_Tab2_103</t>
-  </si>
-  <si>
-    <t>Face</t>
-  </si>
-  <si>
-    <t>脸型</t>
-  </si>
-  <si>
-    <t>Text_Tab2_104</t>
-  </si>
-  <si>
-    <t>Eyes</t>
-  </si>
-  <si>
-    <t>眼睛</t>
-  </si>
-  <si>
-    <t>Text_Tab2_105</t>
-  </si>
-  <si>
-    <t>Eyebrows</t>
-  </si>
-  <si>
-    <t>眉毛</t>
-  </si>
-  <si>
-    <t>Text_Tab2_106</t>
-  </si>
-  <si>
-    <t>Makeup</t>
-  </si>
-  <si>
-    <t>妆容</t>
-  </si>
-  <si>
-    <t>Text_Tab2_107</t>
-  </si>
-  <si>
-    <t>Expression</t>
-  </si>
-  <si>
-    <t>表情</t>
-  </si>
-  <si>
-    <t>Text_Tab2_108</t>
-  </si>
-  <si>
-    <t>Outfit</t>
-  </si>
-  <si>
-    <t>套装</t>
-  </si>
-  <si>
-    <t>Text_Tab2_109</t>
-  </si>
-  <si>
-    <t>Hair</t>
-  </si>
-  <si>
-    <t>头发</t>
-  </si>
-  <si>
-    <t>Text_Tab2_110</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>上衣</t>
-  </si>
-  <si>
-    <t>Text_Tab2_111</t>
-  </si>
-  <si>
-    <t>Bottom</t>
-  </si>
-  <si>
-    <t>下衣</t>
-  </si>
-  <si>
-    <t>Text_Tab2_112</t>
-  </si>
-  <si>
-    <t>Gloves</t>
-  </si>
-  <si>
-    <t>鞋子</t>
-  </si>
-  <si>
-    <t>Text_Tab2_113</t>
-  </si>
-  <si>
-    <t>Shoes</t>
-  </si>
-  <si>
-    <t>手套</t>
-  </si>
-  <si>
-    <t>Text_Tab2_114</t>
-  </si>
-  <si>
-    <t>Pet</t>
-  </si>
-  <si>
-    <t>宠物</t>
-  </si>
-  <si>
-    <t>Text_Tab2_115</t>
-  </si>
-  <si>
-    <t>Accessory</t>
-  </si>
-  <si>
-    <t>饰品</t>
-  </si>
-  <si>
-    <t>Text_Tab2_501</t>
-  </si>
-  <si>
     <t>Text_Tab2_502</t>
   </si>
   <si>
@@ -4766,6 +4769,40 @@
   </si>
   <si>
     <t>全服排行榜</t>
+  </si>
+  <si>
+    <t>Text_Tab3_1048</t>
+  </si>
+  <si>
+    <t>灵宠</t>
+  </si>
+  <si>
+    <t>Text_SaveSuccefully</t>
+  </si>
+  <si>
+    <t>Save Succefully</t>
+  </si>
+  <si>
+    <t>保存穿搭成功</t>
+  </si>
+  <si>
+    <t>Text_SaveCurrentCharacter</t>
+  </si>
+  <si>
+    <t>保存当前穿搭
+（{0}/{1}）</t>
+  </si>
+  <si>
+    <t>Text_MaxSaveCount</t>
+  </si>
+  <si>
+    <t>最多只能保存{0}个</t>
+  </si>
+  <si>
+    <t>Text_DeleteSucceed</t>
+  </si>
+  <si>
+    <t>删除成功</t>
   </si>
 </sst>
 </file>
@@ -4778,7 +4815,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -4824,6 +4861,18 @@
     </font>
     <font>
       <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.8"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -5337,28 +5386,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5367,122 +5407,131 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5578,6 +5627,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -12511,13 +12569,13 @@
       <c r="A407" s="2">
         <v>100065</v>
       </c>
-      <c r="B407" s="2" t="s">
+      <c r="B407" s="31" t="s">
         <v>1183</v>
       </c>
-      <c r="C407" s="1" t="s">
+      <c r="C407" s="31" t="s">
         <v>1184</v>
       </c>
-      <c r="D407" s="1" t="s">
+      <c r="D407" s="31" t="s">
         <v>1185</v>
       </c>
       <c r="E407" s="2"/>
@@ -12526,13 +12584,13 @@
       <c r="A408" s="2">
         <v>100066</v>
       </c>
-      <c r="B408" s="2" t="s">
+      <c r="B408" s="31" t="s">
         <v>1186</v>
       </c>
-      <c r="C408" s="1" t="s">
+      <c r="C408" s="31" t="s">
         <v>1187</v>
       </c>
-      <c r="D408" s="1" t="s">
+      <c r="D408" s="31" t="s">
         <v>1188</v>
       </c>
       <c r="E408" s="2"/>
@@ -12541,13 +12599,13 @@
       <c r="A409" s="2">
         <v>100067</v>
       </c>
-      <c r="B409" s="2" t="s">
+      <c r="B409" s="31" t="s">
         <v>1189</v>
       </c>
-      <c r="C409" s="1" t="s">
+      <c r="C409" s="31" t="s">
         <v>1190</v>
       </c>
-      <c r="D409" s="1" t="s">
+      <c r="D409" s="31" t="s">
         <v>1191</v>
       </c>
       <c r="E409" s="2"/>
@@ -12556,13 +12614,13 @@
       <c r="A410" s="2">
         <v>100068</v>
       </c>
-      <c r="B410" s="2" t="s">
+      <c r="B410" s="31" t="s">
         <v>1192</v>
       </c>
-      <c r="C410" s="1" t="s">
+      <c r="C410" s="31" t="s">
         <v>1193</v>
       </c>
-      <c r="D410" s="1" t="s">
+      <c r="D410" s="31" t="s">
         <v>1194</v>
       </c>
       <c r="E410" s="2"/>
@@ -12571,13 +12629,13 @@
       <c r="A411" s="2">
         <v>100069</v>
       </c>
-      <c r="B411" s="2" t="s">
+      <c r="B411" s="31" t="s">
         <v>1195</v>
       </c>
-      <c r="C411" s="1" t="s">
+      <c r="C411" s="31" t="s">
         <v>1196</v>
       </c>
-      <c r="D411" s="1" t="s">
+      <c r="D411" s="31" t="s">
         <v>1197</v>
       </c>
       <c r="E411" s="2"/>
@@ -12586,13 +12644,13 @@
       <c r="A412" s="2">
         <v>100070</v>
       </c>
-      <c r="B412" s="2" t="s">
+      <c r="B412" s="31" t="s">
         <v>1198</v>
       </c>
-      <c r="C412" s="1" t="s">
+      <c r="C412" s="31" t="s">
         <v>1199</v>
       </c>
-      <c r="D412" s="1" t="s">
+      <c r="D412" s="31" t="s">
         <v>1200</v>
       </c>
       <c r="E412" s="2"/>
@@ -12601,13 +12659,13 @@
       <c r="A413" s="2">
         <v>100071</v>
       </c>
-      <c r="B413" s="2" t="s">
+      <c r="B413" s="31" t="s">
         <v>1201</v>
       </c>
-      <c r="C413" s="1" t="s">
+      <c r="C413" s="31" t="s">
         <v>1202</v>
       </c>
-      <c r="D413" s="1" t="s">
+      <c r="D413" s="31" t="s">
         <v>1203</v>
       </c>
       <c r="E413" s="2"/>
@@ -12616,13 +12674,13 @@
       <c r="A414" s="2">
         <v>100072</v>
       </c>
-      <c r="B414" s="2" t="s">
+      <c r="B414" s="31" t="s">
         <v>1204</v>
       </c>
-      <c r="C414" s="1" t="s">
+      <c r="C414" s="31" t="s">
         <v>1205</v>
       </c>
-      <c r="D414" s="1" t="s">
+      <c r="D414" s="31" t="s">
         <v>1206</v>
       </c>
       <c r="E414" s="2"/>
@@ -12631,13 +12689,13 @@
       <c r="A415" s="2">
         <v>100073</v>
       </c>
-      <c r="B415" s="2" t="s">
+      <c r="B415" s="31" t="s">
         <v>1207</v>
       </c>
-      <c r="C415" s="1" t="s">
+      <c r="C415" s="31" t="s">
         <v>1208</v>
       </c>
-      <c r="D415" s="1" t="s">
+      <c r="D415" s="31" t="s">
         <v>1209</v>
       </c>
       <c r="E415" s="2"/>
@@ -12646,13 +12704,13 @@
       <c r="A416" s="2">
         <v>100074</v>
       </c>
-      <c r="B416" s="2" t="s">
+      <c r="B416" s="31" t="s">
         <v>1210</v>
       </c>
-      <c r="C416" s="1" t="s">
+      <c r="C416" s="31" t="s">
         <v>1211</v>
       </c>
-      <c r="D416" s="1" t="s">
+      <c r="D416" s="31" t="s">
         <v>1212</v>
       </c>
       <c r="E416" s="2"/>
@@ -12661,13 +12719,13 @@
       <c r="A417" s="2">
         <v>100075</v>
       </c>
-      <c r="B417" s="2" t="s">
+      <c r="B417" s="31" t="s">
         <v>1213</v>
       </c>
-      <c r="C417" s="1" t="s">
+      <c r="C417" s="31" t="s">
         <v>1214</v>
       </c>
-      <c r="D417" s="1" t="s">
+      <c r="D417" s="31" t="s">
         <v>1215</v>
       </c>
       <c r="E417" s="2"/>
@@ -12676,13 +12734,13 @@
       <c r="A418" s="2">
         <v>100076</v>
       </c>
-      <c r="B418" s="2" t="s">
+      <c r="B418" s="31" t="s">
         <v>1216</v>
       </c>
-      <c r="C418" s="1" t="s">
+      <c r="C418" s="31" t="s">
         <v>1217</v>
       </c>
-      <c r="D418" s="1" t="s">
+      <c r="D418" s="31" t="s">
         <v>1218</v>
       </c>
       <c r="E418" s="2"/>
@@ -12691,13 +12749,13 @@
       <c r="A419" s="2">
         <v>100077</v>
       </c>
-      <c r="B419" s="2" t="s">
+      <c r="B419" s="31" t="s">
         <v>1219</v>
       </c>
-      <c r="C419" s="1" t="s">
+      <c r="C419" s="31" t="s">
         <v>1220</v>
       </c>
-      <c r="D419" s="1" t="s">
+      <c r="D419" s="31" t="s">
         <v>1221</v>
       </c>
       <c r="E419" s="2"/>
@@ -12706,13 +12764,13 @@
       <c r="A420" s="2">
         <v>100078</v>
       </c>
-      <c r="B420" s="2" t="s">
+      <c r="B420" s="31" t="s">
         <v>1222</v>
       </c>
-      <c r="C420" s="1" t="s">
+      <c r="C420" s="31" t="s">
         <v>1223</v>
       </c>
-      <c r="D420" s="1" t="s">
+      <c r="D420" s="31" t="s">
         <v>1224</v>
       </c>
       <c r="E420" s="2"/>
@@ -12721,13 +12779,13 @@
       <c r="A421" s="2">
         <v>100079</v>
       </c>
-      <c r="B421" s="2" t="s">
+      <c r="B421" s="31" t="s">
         <v>1225</v>
       </c>
-      <c r="C421" s="1" t="s">
+      <c r="C421" s="31" t="s">
         <v>1226</v>
       </c>
-      <c r="D421" s="1" t="s">
+      <c r="D421" s="31" t="s">
         <v>1227</v>
       </c>
       <c r="E421" s="2"/>
@@ -12736,13 +12794,13 @@
       <c r="A422" s="2">
         <v>100080</v>
       </c>
-      <c r="B422" s="2" t="s">
+      <c r="B422" s="31" t="s">
         <v>1228</v>
       </c>
-      <c r="C422" s="1" t="s">
+      <c r="C422" s="31" t="s">
         <v>1229</v>
       </c>
-      <c r="D422" s="1" t="s">
+      <c r="D422" s="31" t="s">
         <v>1230</v>
       </c>
       <c r="E422" s="2"/>
@@ -12751,13 +12809,13 @@
       <c r="A423" s="2">
         <v>100081</v>
       </c>
-      <c r="B423" s="2" t="s">
+      <c r="B423" s="31" t="s">
         <v>1231</v>
       </c>
-      <c r="C423" s="1" t="s">
+      <c r="C423" s="31" t="s">
         <v>1232</v>
       </c>
-      <c r="D423" s="1" t="s">
+      <c r="D423" s="31" t="s">
         <v>1233</v>
       </c>
       <c r="E423" s="2"/>
@@ -12766,13 +12824,13 @@
       <c r="A424" s="2">
         <v>100082</v>
       </c>
-      <c r="B424" s="2" t="s">
+      <c r="B424" s="31" t="s">
         <v>1234</v>
       </c>
-      <c r="C424" s="1" t="s">
+      <c r="C424" s="31" t="s">
         <v>1235</v>
       </c>
-      <c r="D424" s="1" t="s">
+      <c r="D424" s="31" t="s">
         <v>1236</v>
       </c>
       <c r="E424" s="2"/>
@@ -12781,13 +12839,13 @@
       <c r="A425" s="2">
         <v>100083</v>
       </c>
-      <c r="B425" s="2" t="s">
+      <c r="B425" s="31" t="s">
         <v>1237</v>
       </c>
-      <c r="C425" s="1" t="s">
+      <c r="C425" s="31" t="s">
         <v>1238</v>
       </c>
-      <c r="D425" s="1" t="s">
+      <c r="D425" s="31" t="s">
         <v>1239</v>
       </c>
       <c r="E425" s="2"/>
@@ -12806,7 +12864,7 @@
         <v>1197</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -12814,7 +12872,7 @@
         <v>100085</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>1199</v>
@@ -12823,7 +12881,7 @@
         <v>1200</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -12831,7 +12889,7 @@
         <v>100086</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>1202</v>
@@ -12840,7 +12898,7 @@
         <v>1203</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -12848,7 +12906,7 @@
         <v>100087</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>1205</v>
@@ -12857,7 +12915,7 @@
         <v>1206</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -12865,7 +12923,7 @@
         <v>100088</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>1208</v>
@@ -12874,7 +12932,7 @@
         <v>1209</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -12882,7 +12940,7 @@
         <v>100089</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>1211</v>
@@ -12891,7 +12949,7 @@
         <v>1212</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -12899,7 +12957,7 @@
         <v>100090</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>1214</v>
@@ -12908,7 +12966,7 @@
         <v>1215</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -12916,7 +12974,7 @@
         <v>100091</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>1217</v>
@@ -12925,7 +12983,7 @@
         <v>1218</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -12933,7 +12991,7 @@
         <v>100092</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>1220</v>
@@ -12942,7 +13000,7 @@
         <v>1221</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -12950,7 +13008,7 @@
         <v>100093</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>1223</v>
@@ -12959,7 +13017,7 @@
         <v>1224</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -12967,7 +13025,7 @@
         <v>100094</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>1226</v>
@@ -12976,7 +13034,7 @@
         <v>1227</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -12984,7 +13042,7 @@
         <v>100095</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>1229</v>
@@ -12993,7 +13051,7 @@
         <v>1230</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -13001,7 +13059,7 @@
         <v>100096</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>1232</v>
@@ -13010,7 +13068,7 @@
         <v>1233</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -13018,7 +13076,7 @@
         <v>100097</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>1235</v>
@@ -13027,7 +13085,7 @@
         <v>1236</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -13035,7 +13093,7 @@
         <v>100098</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>1238</v>
@@ -13044,21 +13102,21 @@
         <v>1239</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="441" spans="1:5">
       <c r="A441" s="2">
         <v>100099</v>
       </c>
-      <c r="B441" s="2" t="s">
-        <v>1255</v>
-      </c>
-      <c r="C441" s="1" t="s">
+      <c r="B441" s="31" t="s">
         <v>1256</v>
       </c>
-      <c r="D441" s="1" t="s">
+      <c r="C441" s="31" t="s">
         <v>1257</v>
+      </c>
+      <c r="D441" s="31" t="s">
+        <v>1258</v>
       </c>
       <c r="E441" s="2"/>
     </row>
@@ -13066,14 +13124,14 @@
       <c r="A442" s="2">
         <v>100100</v>
       </c>
-      <c r="B442" s="2" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C442" s="1" t="s">
+      <c r="B442" s="31" t="s">
         <v>1259</v>
       </c>
-      <c r="D442" s="1" t="s">
+      <c r="C442" s="31" t="s">
         <v>1260</v>
+      </c>
+      <c r="D442" s="31" t="s">
+        <v>1261</v>
       </c>
       <c r="E442" s="2"/>
     </row>
@@ -13081,14 +13139,14 @@
       <c r="A443" s="2">
         <v>100101</v>
       </c>
-      <c r="B443" s="2" t="s">
-        <v>1261</v>
-      </c>
-      <c r="C443" s="1" t="s">
+      <c r="B443" s="31" t="s">
         <v>1262</v>
       </c>
-      <c r="D443" s="1" t="s">
+      <c r="C443" s="31" t="s">
         <v>1263</v>
+      </c>
+      <c r="D443" s="31" t="s">
+        <v>1264</v>
       </c>
       <c r="E443" s="2"/>
     </row>
@@ -13096,14 +13154,14 @@
       <c r="A444" s="2">
         <v>100102</v>
       </c>
-      <c r="B444" s="2" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C444" s="1" t="s">
+      <c r="B444" s="31" t="s">
         <v>1265</v>
       </c>
-      <c r="D444" s="1" t="s">
+      <c r="C444" s="31" t="s">
         <v>1266</v>
+      </c>
+      <c r="D444" s="31" t="s">
+        <v>1267</v>
       </c>
       <c r="E444" s="2"/>
     </row>
@@ -13111,14 +13169,14 @@
       <c r="A445" s="2">
         <v>100103</v>
       </c>
-      <c r="B445" s="2" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C445" s="1" t="s">
+      <c r="B445" s="31" t="s">
         <v>1268</v>
       </c>
-      <c r="D445" s="1" t="s">
+      <c r="C445" s="31" t="s">
         <v>1269</v>
+      </c>
+      <c r="D445" s="31" t="s">
+        <v>1270</v>
       </c>
       <c r="E445" s="2"/>
     </row>
@@ -13126,14 +13184,14 @@
       <c r="A446" s="2">
         <v>100104</v>
       </c>
-      <c r="B446" s="2" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C446" s="1" t="s">
+      <c r="B446" s="31" t="s">
         <v>1271</v>
       </c>
-      <c r="D446" s="1" t="s">
+      <c r="C446" s="31" t="s">
         <v>1272</v>
+      </c>
+      <c r="D446" s="31" t="s">
+        <v>1273</v>
       </c>
       <c r="E446" s="2"/>
     </row>
@@ -13141,14 +13199,14 @@
       <c r="A447" s="2">
         <v>100105</v>
       </c>
-      <c r="B447" s="2" t="s">
-        <v>1273</v>
-      </c>
-      <c r="C447" s="1" t="s">
+      <c r="B447" s="31" t="s">
         <v>1274</v>
       </c>
-      <c r="D447" s="1" t="s">
+      <c r="C447" s="31" t="s">
         <v>1275</v>
+      </c>
+      <c r="D447" s="31" t="s">
+        <v>1276</v>
       </c>
       <c r="E447" s="2"/>
     </row>
@@ -13156,14 +13214,14 @@
       <c r="A448" s="2">
         <v>100106</v>
       </c>
-      <c r="B448" s="2" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C448" s="1" t="s">
+      <c r="B448" s="31" t="s">
         <v>1277</v>
       </c>
-      <c r="D448" s="1" t="s">
+      <c r="C448" s="31" t="s">
         <v>1278</v>
+      </c>
+      <c r="D448" s="31" t="s">
+        <v>1279</v>
       </c>
       <c r="E448" s="2"/>
     </row>
@@ -13171,14 +13229,14 @@
       <c r="A449" s="2">
         <v>100107</v>
       </c>
-      <c r="B449" s="2" t="s">
-        <v>1279</v>
-      </c>
-      <c r="C449" s="1" t="s">
+      <c r="B449" s="31" t="s">
         <v>1280</v>
       </c>
-      <c r="D449" s="1" t="s">
+      <c r="C449" s="31" t="s">
         <v>1281</v>
+      </c>
+      <c r="D449" s="31" t="s">
+        <v>1282</v>
       </c>
       <c r="E449" s="2"/>
     </row>
@@ -13186,14 +13244,14 @@
       <c r="A450" s="2">
         <v>100108</v>
       </c>
-      <c r="B450" s="2" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C450" s="1" t="s">
+      <c r="B450" s="31" t="s">
         <v>1283</v>
       </c>
-      <c r="D450" s="1" t="s">
+      <c r="C450" s="31" t="s">
         <v>1284</v>
+      </c>
+      <c r="D450" s="31" t="s">
+        <v>1285</v>
       </c>
       <c r="E450" s="2"/>
     </row>
@@ -13201,14 +13259,14 @@
       <c r="A451" s="2">
         <v>100109</v>
       </c>
-      <c r="B451" s="2" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C451" s="1" t="s">
+      <c r="B451" s="31" t="s">
         <v>1286</v>
       </c>
-      <c r="D451" s="1" t="s">
+      <c r="C451" s="31" t="s">
         <v>1287</v>
+      </c>
+      <c r="D451" s="31" t="s">
+        <v>1288</v>
       </c>
       <c r="E451" s="2"/>
     </row>
@@ -13216,14 +13274,14 @@
       <c r="A452" s="2">
         <v>100110</v>
       </c>
-      <c r="B452" s="2" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C452" s="1" t="s">
+      <c r="B452" s="31" t="s">
         <v>1289</v>
       </c>
-      <c r="D452" s="1" t="s">
+      <c r="C452" s="31" t="s">
         <v>1290</v>
+      </c>
+      <c r="D452" s="31" t="s">
+        <v>1291</v>
       </c>
       <c r="E452" s="2"/>
     </row>
@@ -13231,14 +13289,14 @@
       <c r="A453" s="2">
         <v>100111</v>
       </c>
-      <c r="B453" s="2" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C453" s="1" t="s">
+      <c r="B453" s="31" t="s">
         <v>1292</v>
       </c>
-      <c r="D453" s="1" t="s">
+      <c r="C453" s="31" t="s">
         <v>1293</v>
+      </c>
+      <c r="D453" s="31" t="s">
+        <v>1294</v>
       </c>
       <c r="E453" s="2"/>
     </row>
@@ -13246,14 +13304,14 @@
       <c r="A454" s="2">
         <v>100112</v>
       </c>
-      <c r="B454" s="2" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C454" s="1" t="s">
+      <c r="B454" s="31" t="s">
         <v>1295</v>
       </c>
-      <c r="D454" s="1" t="s">
+      <c r="C454" s="31" t="s">
         <v>1296</v>
+      </c>
+      <c r="D454" s="31" t="s">
+        <v>1297</v>
       </c>
       <c r="E454" s="2"/>
     </row>
@@ -13261,14 +13319,14 @@
       <c r="A455" s="2">
         <v>100113</v>
       </c>
-      <c r="B455" s="2" t="s">
-        <v>1297</v>
-      </c>
-      <c r="C455" s="1" t="s">
+      <c r="B455" s="31" t="s">
         <v>1298</v>
       </c>
-      <c r="D455" s="1" t="s">
+      <c r="C455" s="31" t="s">
         <v>1299</v>
+      </c>
+      <c r="D455" s="31" t="s">
+        <v>1300</v>
       </c>
       <c r="E455" s="2"/>
     </row>
@@ -13276,14 +13334,14 @@
       <c r="A456" s="2">
         <v>100114</v>
       </c>
-      <c r="B456" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C456" s="1" t="s">
+      <c r="B456" s="31" t="s">
         <v>1301</v>
       </c>
-      <c r="D456" s="1" t="s">
+      <c r="C456" s="31" t="s">
         <v>1302</v>
+      </c>
+      <c r="D456" s="31" t="s">
+        <v>1303</v>
       </c>
       <c r="E456" s="2"/>
     </row>
@@ -13291,14 +13349,14 @@
       <c r="A457" s="2">
         <v>100115</v>
       </c>
-      <c r="B457" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C457" s="1" t="s">
+      <c r="B457" s="31" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C457" s="31" t="s">
         <v>1202</v>
       </c>
-      <c r="D457" s="1" t="s">
-        <v>1304</v>
+      <c r="D457" s="31" t="s">
+        <v>1305</v>
       </c>
       <c r="E457" s="2"/>
     </row>
@@ -13306,14 +13364,14 @@
       <c r="A458" s="2">
         <v>100116</v>
       </c>
-      <c r="B458" s="2" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C458" s="1" t="s">
+      <c r="B458" s="31" t="s">
         <v>1306</v>
       </c>
-      <c r="D458" s="1" t="s">
+      <c r="C458" s="31" t="s">
         <v>1307</v>
+      </c>
+      <c r="D458" s="31" t="s">
+        <v>1308</v>
       </c>
       <c r="E458" s="2"/>
     </row>
@@ -13321,14 +13379,14 @@
       <c r="A459" s="2">
         <v>100117</v>
       </c>
-      <c r="B459" s="2" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C459" s="1" t="s">
+      <c r="B459" s="31" t="s">
         <v>1309</v>
       </c>
-      <c r="D459" s="1" t="s">
+      <c r="C459" s="31" t="s">
         <v>1310</v>
+      </c>
+      <c r="D459" s="31" t="s">
+        <v>1311</v>
       </c>
       <c r="E459" s="2"/>
     </row>
@@ -13336,14 +13394,14 @@
       <c r="A460" s="2">
         <v>100118</v>
       </c>
-      <c r="B460" s="2" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C460" s="1" t="s">
+      <c r="B460" s="31" t="s">
         <v>1312</v>
       </c>
-      <c r="D460" s="1" t="s">
+      <c r="C460" s="31" t="s">
         <v>1313</v>
+      </c>
+      <c r="D460" s="31" t="s">
+        <v>1314</v>
       </c>
       <c r="E460" s="2"/>
     </row>
@@ -13352,16 +13410,16 @@
         <v>100119</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -13369,16 +13427,16 @@
         <v>100120</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -13386,16 +13444,16 @@
         <v>100121</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -13403,16 +13461,16 @@
         <v>100122</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -13420,16 +13478,16 @@
         <v>100123</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -13437,16 +13495,16 @@
         <v>100124</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -13454,16 +13512,16 @@
         <v>100125</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -13471,16 +13529,16 @@
         <v>100126</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -13488,16 +13546,16 @@
         <v>100127</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -13505,16 +13563,16 @@
         <v>100128</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -13522,16 +13580,16 @@
         <v>100129</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -13539,16 +13597,16 @@
         <v>100130</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -13556,16 +13614,16 @@
         <v>100131</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -13573,16 +13631,16 @@
         <v>100132</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -13590,16 +13648,16 @@
         <v>100133</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -13607,16 +13665,16 @@
         <v>100134</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C476" s="1" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -13624,16 +13682,16 @@
         <v>100135</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>1202</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -13641,16 +13699,16 @@
         <v>100136</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -13658,16 +13716,16 @@
         <v>100137</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -13675,16 +13733,16 @@
         <v>100138</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -13692,13 +13750,13 @@
         <v>100139</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>181</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="E481" s="2"/>
     </row>
@@ -13707,13 +13765,13 @@
         <v>100140</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>1178</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="E482" s="2"/>
     </row>
@@ -13722,13 +13780,13 @@
         <v>100141</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E483" s="2"/>
     </row>
@@ -13737,13 +13795,13 @@
         <v>100142</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="E484" s="2"/>
     </row>
@@ -13752,13 +13810,13 @@
         <v>100143</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="E485" s="2"/>
     </row>
@@ -13767,13 +13825,13 @@
         <v>100144</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="E486" s="2"/>
     </row>
@@ -13782,13 +13840,13 @@
         <v>100145</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="E487" s="2"/>
     </row>
@@ -13797,13 +13855,13 @@
         <v>100146</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="E488" s="2"/>
     </row>
@@ -13812,13 +13870,13 @@
         <v>100147</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="E489" s="2"/>
     </row>
@@ -13827,13 +13885,13 @@
         <v>100148</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="E490" s="2"/>
     </row>
@@ -13842,13 +13900,13 @@
         <v>100149</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="E491" s="2"/>
     </row>
@@ -13857,13 +13915,13 @@
         <v>100150</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="E492" s="2"/>
     </row>
@@ -13872,13 +13930,13 @@
         <v>100151</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="E493" s="2"/>
     </row>
@@ -13887,13 +13945,13 @@
         <v>100152</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E494" s="2"/>
     </row>
@@ -13902,10 +13960,10 @@
         <v>100153</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D495" s="1" t="s">
         <v>237</v>
@@ -13917,16 +13975,16 @@
         <v>100154</v>
       </c>
       <c r="B496" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C496" s="1" t="s">
         <v>1378</v>
-      </c>
-      <c r="C496" s="1" t="s">
-        <v>1377</v>
       </c>
       <c r="D496" s="1" t="s">
         <v>237</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>1191</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -13934,13 +13992,13 @@
         <v>100155</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E497" s="2"/>
     </row>
@@ -13949,13 +14007,13 @@
         <v>100156</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="E498" s="2"/>
     </row>
@@ -13964,13 +14022,13 @@
         <v>100157</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="E499" s="2"/>
     </row>
@@ -13979,13 +14037,13 @@
         <v>100158</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="E500" s="2"/>
     </row>
@@ -13994,13 +14052,13 @@
         <v>100159</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="E501" s="2"/>
     </row>
@@ -14009,13 +14067,13 @@
         <v>100160</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="E502" s="2"/>
     </row>
@@ -14024,13 +14082,13 @@
         <v>100161</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="E503" s="2"/>
     </row>
@@ -14039,13 +14097,13 @@
         <v>100162</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="E504" s="2"/>
     </row>
@@ -14054,13 +14112,13 @@
         <v>100163</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="E505" s="2"/>
     </row>
@@ -14069,13 +14127,13 @@
         <v>100164</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="E506" s="2"/>
     </row>
@@ -14084,13 +14142,13 @@
         <v>100165</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="E507" s="2"/>
     </row>
@@ -14099,13 +14157,13 @@
         <v>100166</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="E508" s="2"/>
     </row>
@@ -14114,13 +14172,13 @@
         <v>100167</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="E509" s="2"/>
     </row>
@@ -14129,13 +14187,13 @@
         <v>100168</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="E510" s="2"/>
     </row>
@@ -14144,13 +14202,13 @@
         <v>100169</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="E511" s="2"/>
     </row>
@@ -14159,13 +14217,13 @@
         <v>100170</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E512" s="2"/>
     </row>
@@ -14174,13 +14232,13 @@
         <v>100171</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="E513" s="2"/>
     </row>
@@ -14189,13 +14247,13 @@
         <v>100172</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="E514" s="2"/>
     </row>
@@ -14204,13 +14262,13 @@
         <v>100173</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="E515" s="2"/>
     </row>
@@ -14219,13 +14277,13 @@
         <v>100174</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="E516" s="2"/>
     </row>
@@ -14234,13 +14292,13 @@
         <v>100175</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="E517" s="2"/>
     </row>
@@ -14249,13 +14307,13 @@
         <v>100176</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="E518" s="2"/>
     </row>
@@ -14264,13 +14322,13 @@
         <v>100177</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="E519" s="2"/>
     </row>
@@ -14279,13 +14337,13 @@
         <v>100178</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="C520" s="1" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="E520" s="2"/>
     </row>
@@ -14294,13 +14352,13 @@
         <v>100179</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="E521" s="2"/>
     </row>
@@ -14309,13 +14367,13 @@
         <v>100180</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="E522" s="2"/>
     </row>
@@ -14324,13 +14382,13 @@
         <v>100181</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="E523" s="2"/>
     </row>
@@ -14339,13 +14397,13 @@
         <v>100182</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="E524" s="2"/>
     </row>
@@ -14354,13 +14412,13 @@
         <v>100183</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="E525" s="2"/>
     </row>
@@ -14369,13 +14427,13 @@
         <v>100184</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="E526" s="2"/>
     </row>
@@ -14384,13 +14442,13 @@
         <v>100185</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="E527" s="2"/>
     </row>
@@ -14398,14 +14456,14 @@
       <c r="A528" s="2">
         <v>100186</v>
       </c>
-      <c r="B528" s="2" t="s">
-        <v>1472</v>
-      </c>
-      <c r="C528" s="1" t="s">
+      <c r="B528" s="31" t="s">
         <v>1473</v>
       </c>
-      <c r="D528" s="1" t="s">
+      <c r="C528" s="31" t="s">
         <v>1474</v>
+      </c>
+      <c r="D528" s="31" t="s">
+        <v>1475</v>
       </c>
       <c r="E528" s="2"/>
     </row>
@@ -14413,14 +14471,14 @@
       <c r="A529" s="2">
         <v>100187</v>
       </c>
-      <c r="B529" s="2" t="s">
-        <v>1475</v>
-      </c>
-      <c r="C529" s="1" t="s">
+      <c r="B529" s="31" t="s">
         <v>1476</v>
       </c>
-      <c r="D529" s="1" t="s">
+      <c r="C529" s="31" t="s">
         <v>1477</v>
+      </c>
+      <c r="D529" s="31" t="s">
+        <v>1478</v>
       </c>
       <c r="E529" s="2"/>
     </row>
@@ -14428,14 +14486,14 @@
       <c r="A530" s="2">
         <v>100188</v>
       </c>
-      <c r="B530" s="2" t="s">
-        <v>1478</v>
-      </c>
-      <c r="C530" s="1" t="s">
+      <c r="B530" s="31" t="s">
         <v>1479</v>
       </c>
-      <c r="D530" s="1" t="s">
+      <c r="C530" s="31" t="s">
         <v>1480</v>
+      </c>
+      <c r="D530" s="31" t="s">
+        <v>1481</v>
       </c>
       <c r="E530" s="2"/>
     </row>
@@ -14443,14 +14501,14 @@
       <c r="A531" s="2">
         <v>100189</v>
       </c>
-      <c r="B531" s="2" t="s">
-        <v>1481</v>
-      </c>
-      <c r="C531" s="1" t="s">
+      <c r="B531" s="31" t="s">
         <v>1482</v>
       </c>
-      <c r="D531" s="1" t="s">
+      <c r="C531" s="31" t="s">
         <v>1483</v>
+      </c>
+      <c r="D531" s="31" t="s">
+        <v>1484</v>
       </c>
       <c r="E531" s="2"/>
     </row>
@@ -14458,14 +14516,14 @@
       <c r="A532" s="2">
         <v>100190</v>
       </c>
-      <c r="B532" s="2" t="s">
-        <v>1484</v>
-      </c>
-      <c r="C532" s="1" t="s">
+      <c r="B532" s="31" t="s">
         <v>1485</v>
       </c>
-      <c r="D532" s="1" t="s">
+      <c r="C532" s="31" t="s">
         <v>1486</v>
+      </c>
+      <c r="D532" s="31" t="s">
+        <v>1487</v>
       </c>
       <c r="E532" s="2"/>
     </row>
@@ -14473,14 +14531,14 @@
       <c r="A533" s="2">
         <v>100191</v>
       </c>
-      <c r="B533" s="2" t="s">
-        <v>1487</v>
-      </c>
-      <c r="C533" s="1" t="s">
+      <c r="B533" s="31" t="s">
         <v>1488</v>
       </c>
-      <c r="D533" s="1" t="s">
+      <c r="C533" s="32" t="s">
         <v>1489</v>
+      </c>
+      <c r="D533" s="32" t="s">
+        <v>1490</v>
       </c>
       <c r="E533" s="2"/>
     </row>
@@ -14488,14 +14546,14 @@
       <c r="A534" s="2">
         <v>100192</v>
       </c>
-      <c r="B534" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="C534" s="1" t="s">
+      <c r="B534" s="31" t="s">
         <v>1491</v>
       </c>
-      <c r="D534" s="1" t="s">
+      <c r="C534" s="32" t="s">
         <v>1492</v>
+      </c>
+      <c r="D534" s="32" t="s">
+        <v>1493</v>
       </c>
       <c r="E534" s="2"/>
     </row>
@@ -14503,14 +14561,14 @@
       <c r="A535" s="2">
         <v>100193</v>
       </c>
-      <c r="B535" s="2" t="s">
-        <v>1493</v>
-      </c>
-      <c r="C535" s="1" t="s">
+      <c r="B535" s="32" t="s">
         <v>1494</v>
       </c>
-      <c r="D535" s="1" t="s">
+      <c r="C535" s="32" t="s">
         <v>1495</v>
+      </c>
+      <c r="D535" s="32" t="s">
+        <v>1496</v>
       </c>
       <c r="E535" s="2"/>
     </row>
@@ -14518,14 +14576,14 @@
       <c r="A536" s="2">
         <v>100194</v>
       </c>
-      <c r="B536" s="2" t="s">
-        <v>1496</v>
-      </c>
-      <c r="C536" s="1" t="s">
+      <c r="B536" s="32" t="s">
         <v>1497</v>
       </c>
-      <c r="D536" s="1" t="s">
+      <c r="C536" s="32" t="s">
         <v>1498</v>
+      </c>
+      <c r="D536" s="32" t="s">
+        <v>1499</v>
       </c>
       <c r="E536" s="2"/>
     </row>
@@ -14533,14 +14591,14 @@
       <c r="A537" s="2">
         <v>100195</v>
       </c>
-      <c r="B537" s="2" t="s">
-        <v>1499</v>
-      </c>
-      <c r="C537" s="1" t="s">
+      <c r="B537" s="32" t="s">
         <v>1500</v>
       </c>
-      <c r="D537" s="1" t="s">
+      <c r="C537" s="32" t="s">
         <v>1501</v>
+      </c>
+      <c r="D537" s="32" t="s">
+        <v>1502</v>
       </c>
       <c r="E537" s="2"/>
     </row>
@@ -14548,13 +14606,13 @@
       <c r="A538" s="2">
         <v>100196</v>
       </c>
-      <c r="B538" s="2" t="s">
-        <v>1502</v>
-      </c>
-      <c r="C538" s="1" t="s">
+      <c r="B538" s="32" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C538" s="32" t="s">
         <v>1217</v>
       </c>
-      <c r="D538" s="1" t="s">
+      <c r="D538" s="32" t="s">
         <v>1218</v>
       </c>
       <c r="E538" s="2"/>
@@ -14563,14 +14621,14 @@
       <c r="A539" s="2">
         <v>100197</v>
       </c>
-      <c r="B539" s="2" t="s">
-        <v>1503</v>
-      </c>
-      <c r="C539" s="1" t="s">
+      <c r="B539" s="32" t="s">
         <v>1504</v>
       </c>
-      <c r="D539" s="1" t="s">
+      <c r="C539" s="32" t="s">
         <v>1505</v>
+      </c>
+      <c r="D539" s="32" t="s">
+        <v>1506</v>
       </c>
       <c r="E539" s="2"/>
     </row>
@@ -14578,14 +14636,14 @@
       <c r="A540" s="2">
         <v>100198</v>
       </c>
-      <c r="B540" s="2" t="s">
-        <v>1506</v>
-      </c>
-      <c r="C540" s="1" t="s">
+      <c r="B540" s="32" t="s">
         <v>1507</v>
       </c>
-      <c r="D540" s="1" t="s">
+      <c r="C540" s="32" t="s">
         <v>1508</v>
+      </c>
+      <c r="D540" s="32" t="s">
+        <v>1509</v>
       </c>
       <c r="E540" s="2"/>
     </row>
@@ -14593,14 +14651,14 @@
       <c r="A541" s="2">
         <v>100199</v>
       </c>
-      <c r="B541" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="C541" s="1" t="s">
+      <c r="B541" s="32" t="s">
         <v>1510</v>
       </c>
-      <c r="D541" s="1" t="s">
+      <c r="C541" s="32" t="s">
         <v>1511</v>
+      </c>
+      <c r="D541" s="32" t="s">
+        <v>1512</v>
       </c>
       <c r="E541" s="2"/>
     </row>
@@ -14608,14 +14666,14 @@
       <c r="A542" s="2">
         <v>100200</v>
       </c>
-      <c r="B542" s="2" t="s">
-        <v>1512</v>
-      </c>
-      <c r="C542" s="1" t="s">
+      <c r="B542" s="32" t="s">
         <v>1513</v>
       </c>
-      <c r="D542" s="1" t="s">
+      <c r="C542" s="32" t="s">
         <v>1514</v>
+      </c>
+      <c r="D542" s="32" t="s">
+        <v>1515</v>
       </c>
       <c r="E542" s="2"/>
     </row>
@@ -14623,14 +14681,14 @@
       <c r="A543" s="2">
         <v>100201</v>
       </c>
-      <c r="B543" s="2" t="s">
-        <v>1515</v>
-      </c>
-      <c r="C543" s="1" t="s">
+      <c r="B543" s="32" t="s">
         <v>1516</v>
       </c>
-      <c r="D543" s="1" t="s">
+      <c r="C543" s="32" t="s">
         <v>1517</v>
+      </c>
+      <c r="D543" s="32" t="s">
+        <v>1518</v>
       </c>
       <c r="E543" s="2"/>
     </row>
@@ -14638,14 +14696,14 @@
       <c r="A544" s="2">
         <v>100202</v>
       </c>
-      <c r="B544" s="2" t="s">
-        <v>1518</v>
-      </c>
-      <c r="C544" s="1" t="s">
+      <c r="B544" s="32" t="s">
         <v>1519</v>
       </c>
-      <c r="D544" s="1" t="s">
+      <c r="C544" s="32" t="s">
         <v>1520</v>
+      </c>
+      <c r="D544" s="32" t="s">
+        <v>1521</v>
       </c>
       <c r="E544" s="2"/>
     </row>
@@ -14653,13 +14711,13 @@
       <c r="A545" s="2">
         <v>100203</v>
       </c>
-      <c r="B545" s="2" t="s">
-        <v>1521</v>
-      </c>
-      <c r="C545" s="1" t="s">
+      <c r="B545" s="32" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C545" s="32" t="s">
         <v>1229</v>
       </c>
-      <c r="D545" s="1" t="s">
+      <c r="D545" s="32" t="s">
         <v>1233</v>
       </c>
       <c r="E545" s="2"/>
@@ -14668,14 +14726,14 @@
       <c r="A546" s="2">
         <v>100204</v>
       </c>
-      <c r="B546" s="2" t="s">
-        <v>1522</v>
-      </c>
-      <c r="C546" s="1" t="s">
+      <c r="B546" s="32" t="s">
         <v>1523</v>
       </c>
-      <c r="D546" s="1" t="s">
+      <c r="C546" s="32" t="s">
         <v>1524</v>
+      </c>
+      <c r="D546" s="32" t="s">
+        <v>1525</v>
       </c>
       <c r="E546" s="2"/>
     </row>
@@ -14683,14 +14741,14 @@
       <c r="A547" s="2">
         <v>100205</v>
       </c>
-      <c r="B547" s="2" t="s">
-        <v>1525</v>
-      </c>
-      <c r="C547" s="1" t="s">
+      <c r="B547" s="32" t="s">
         <v>1526</v>
       </c>
-      <c r="D547" s="1" t="s">
+      <c r="C547" s="32" t="s">
         <v>1527</v>
+      </c>
+      <c r="D547" s="32" t="s">
+        <v>1528</v>
       </c>
       <c r="E547" s="2"/>
     </row>
@@ -14698,14 +14756,14 @@
       <c r="A548" s="2">
         <v>100206</v>
       </c>
-      <c r="B548" s="2" t="s">
-        <v>1528</v>
-      </c>
-      <c r="C548" s="1" t="s">
+      <c r="B548" s="32" t="s">
         <v>1529</v>
       </c>
-      <c r="D548" s="1" t="s">
+      <c r="C548" s="32" t="s">
         <v>1530</v>
+      </c>
+      <c r="D548" s="32" t="s">
+        <v>1531</v>
       </c>
       <c r="E548" s="2"/>
     </row>
@@ -14713,14 +14771,14 @@
       <c r="A549" s="2">
         <v>100207</v>
       </c>
-      <c r="B549" s="2" t="s">
-        <v>1531</v>
-      </c>
-      <c r="C549" s="1" t="s">
+      <c r="B549" s="32" t="s">
         <v>1532</v>
       </c>
-      <c r="D549" s="1" t="s">
+      <c r="C549" s="32" t="s">
         <v>1533</v>
+      </c>
+      <c r="D549" s="32" t="s">
+        <v>1534</v>
       </c>
       <c r="E549" s="2"/>
     </row>
@@ -14728,14 +14786,14 @@
       <c r="A550" s="2">
         <v>100208</v>
       </c>
-      <c r="B550" s="2" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C550" s="1" t="s">
+      <c r="B550" s="32" t="s">
         <v>1535</v>
       </c>
-      <c r="D550" s="1" t="s">
+      <c r="C550" s="32" t="s">
         <v>1536</v>
+      </c>
+      <c r="D550" s="32" t="s">
+        <v>1537</v>
       </c>
       <c r="E550" s="2"/>
     </row>
@@ -14743,14 +14801,14 @@
       <c r="A551" s="2">
         <v>100209</v>
       </c>
-      <c r="B551" s="2" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C551" s="1" t="s">
+      <c r="B551" s="32" t="s">
         <v>1538</v>
       </c>
-      <c r="D551" s="1" t="s">
+      <c r="C551" s="32" t="s">
         <v>1539</v>
+      </c>
+      <c r="D551" s="32" t="s">
+        <v>1540</v>
       </c>
       <c r="E551" s="2"/>
     </row>
@@ -14758,14 +14816,14 @@
       <c r="A552" s="2">
         <v>100210</v>
       </c>
-      <c r="B552" s="2" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C552" s="1" t="s">
+      <c r="B552" s="32" t="s">
         <v>1541</v>
       </c>
-      <c r="D552" s="1" t="s">
+      <c r="C552" s="32" t="s">
         <v>1542</v>
+      </c>
+      <c r="D552" s="32" t="s">
+        <v>1543</v>
       </c>
       <c r="E552" s="2"/>
     </row>
@@ -14773,14 +14831,14 @@
       <c r="A553" s="2">
         <v>100211</v>
       </c>
-      <c r="B553" s="2" t="s">
-        <v>1543</v>
-      </c>
-      <c r="C553" s="1" t="s">
-        <v>1473</v>
-      </c>
-      <c r="D553" s="1" t="s">
+      <c r="B553" s="31" t="s">
         <v>1544</v>
+      </c>
+      <c r="C553" s="31" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D553" s="31" t="s">
+        <v>1545</v>
       </c>
       <c r="E553" s="2"/>
     </row>
@@ -14789,13 +14847,13 @@
         <v>100212</v>
       </c>
       <c r="B554" s="31" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="C554" s="31" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="D554" s="31" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="E554" s="2"/>
     </row>
@@ -14804,7 +14862,7 @@
         <v>100213</v>
       </c>
       <c r="B555" s="31" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="C555" s="31" t="s">
         <v>1072</v>
@@ -14819,10 +14877,10 @@
         <v>100214</v>
       </c>
       <c r="B556" s="31" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="C556" s="31" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="D556" s="31" t="s">
         <v>1076</v>
@@ -14834,13 +14892,13 @@
         <v>100215</v>
       </c>
       <c r="B557" s="31" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="C557" s="31" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="D557" s="31" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="E557" s="2"/>
     </row>
@@ -14849,13 +14907,13 @@
         <v>100216</v>
       </c>
       <c r="B558" s="31" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="C558" s="31" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="D558" s="31" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="E558" s="2"/>
     </row>
@@ -14864,13 +14922,13 @@
         <v>100217</v>
       </c>
       <c r="B559" s="31" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="C559" s="31" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="D559" s="31" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="E559" s="2"/>
     </row>
@@ -14879,47 +14937,81 @@
         <v>100218</v>
       </c>
       <c r="B560" s="31" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C560" s="1"/>
       <c r="D560" s="1" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="E560" s="2"/>
     </row>
     <row r="561" spans="1:5">
-      <c r="A561" s="2"/>
-      <c r="B561" s="2"/>
-      <c r="C561" s="1"/>
-      <c r="D561" s="1"/>
+      <c r="A561" s="2">
+        <v>100219</v>
+      </c>
+      <c r="B561" s="31" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C561" s="31" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D561" s="31" t="s">
+        <v>1564</v>
+      </c>
       <c r="E561" s="2"/>
     </row>
     <row r="562" spans="1:5">
-      <c r="A562" s="2"/>
-      <c r="B562" s="2"/>
-      <c r="C562" s="1"/>
-      <c r="D562" s="1"/>
+      <c r="A562" s="2">
+        <v>100220</v>
+      </c>
+      <c r="B562" s="31" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C562" s="33" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D562" s="32" t="s">
+        <v>1567</v>
+      </c>
       <c r="E562" s="2"/>
     </row>
-    <row r="563" spans="1:5">
-      <c r="A563" s="2"/>
-      <c r="B563" s="2"/>
-      <c r="C563" s="1"/>
-      <c r="D563" s="1"/>
+    <row r="563" ht="24" spans="1:5">
+      <c r="A563" s="2">
+        <v>100221</v>
+      </c>
+      <c r="B563" s="31" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C563" s="32"/>
+      <c r="D563" s="34" t="s">
+        <v>1569</v>
+      </c>
       <c r="E563" s="2"/>
     </row>
     <row r="564" spans="1:5">
-      <c r="A564" s="2"/>
-      <c r="B564" s="2"/>
-      <c r="C564" s="1"/>
-      <c r="D564" s="1"/>
+      <c r="A564" s="2">
+        <v>100222</v>
+      </c>
+      <c r="B564" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C564" s="32"/>
+      <c r="D564" s="32" t="s">
+        <v>1571</v>
+      </c>
       <c r="E564" s="2"/>
     </row>
     <row r="565" spans="1:5">
-      <c r="A565" s="2"/>
-      <c r="B565" s="2"/>
-      <c r="C565" s="1"/>
-      <c r="D565" s="1"/>
+      <c r="A565" s="2">
+        <v>100223</v>
+      </c>
+      <c r="B565" s="31" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C565" s="32"/>
+      <c r="D565" s="32" t="s">
+        <v>1573</v>
+      </c>
       <c r="E565" s="2"/>
     </row>
     <row r="566" spans="1:5">
